--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="552">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23</t>
+    <t>2025-12-11</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,6 +127,9 @@
     <t>Abstract</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Derivation</t>
   </si>
   <si>
@@ -1220,10 +1223,14 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>Bedeutung: Erfasster Wert der Observation.</t>
+    <t>**Begründung Must-Support:** Erfasster Wert der Observation.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1240,6 +1247,31 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>**Begründung Must-Support:** Zeitpunktbezogene Lebenszustände (z. B. erwarteter Entbindungstermin) benötigen eine eindeutige Datumsangabe als Wert.</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>**Begründung Must-Support:** Viele Lebenszustände (z. B. Schwangerschaftsstatus, Alkoholabusus, Raucherstatus) werden als kategorisierte Angaben kodiert und erfordern daher ein CodeableConcept.</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2031,15 +2063,15 @@
         <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2049,12 +2081,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2097,130 +2129,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
@@ -2232,14 +2264,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>17</v>
@@ -2251,16 +2283,16 @@
         <v>17</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2313,28 +2345,28 @@
         <v>27</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>17</v>
@@ -2345,10 +2377,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2356,31 +2388,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2430,13 +2462,13 @@
         <v>17</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>17</v>
@@ -2465,10 +2497,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2476,10 +2508,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>17</v>
@@ -2488,16 +2520,16 @@
         <v>17</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2548,19 +2580,19 @@
         <v>17</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>17</v>
@@ -2583,10 +2615,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2594,10 +2626,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>17</v>
@@ -2609,13 +2641,13 @@
         <v>17</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2666,13 +2698,13 @@
         <v>17</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>17</v>
@@ -2690,7 +2722,7 @@
         <v>17</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>17</v>
@@ -2701,21 +2733,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -2727,16 +2759,16 @@
         <v>17</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2774,31 +2806,31 @@
         <v>17</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>17</v>
@@ -2810,7 +2842,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>17</v>
@@ -2821,10 +2853,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2832,10 +2864,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>17</v>
@@ -2844,19 +2876,19 @@
         <v>17</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2906,19 +2938,19 @@
         <v>17</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>17</v>
@@ -2941,10 +2973,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2952,10 +2984,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>17</v>
@@ -2964,19 +2996,19 @@
         <v>17</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3026,19 +3058,19 @@
         <v>17</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>17</v>
@@ -3061,10 +3093,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3072,10 +3104,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>17</v>
@@ -3084,19 +3116,19 @@
         <v>17</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3146,19 +3178,19 @@
         <v>17</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>17</v>
@@ -3181,10 +3213,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3192,10 +3224,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>17</v>
@@ -3204,19 +3236,19 @@
         <v>17</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3266,19 +3298,19 @@
         <v>17</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>17</v>
@@ -3301,10 +3333,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3312,10 +3344,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>17</v>
@@ -3324,19 +3356,19 @@
         <v>17</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3362,13 +3394,13 @@
         <v>17</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>17</v>
@@ -3386,19 +3418,19 @@
         <v>17</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>17</v>
@@ -3421,10 +3453,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3432,10 +3464,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>17</v>
@@ -3444,19 +3476,19 @@
         <v>17</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3482,13 +3514,13 @@
         <v>17</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>17</v>
@@ -3506,19 +3538,19 @@
         <v>17</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>17</v>
@@ -3541,10 +3573,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3552,31 +3584,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3626,19 +3658,19 @@
         <v>17</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>17</v>
@@ -3661,10 +3693,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3672,10 +3704,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>17</v>
@@ -3687,16 +3719,16 @@
         <v>17</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3722,13 +3754,13 @@
         <v>17</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>17</v>
@@ -3746,19 +3778,19 @@
         <v>17</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>17</v>
@@ -3781,21 +3813,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>17</v>
@@ -3807,16 +3839,16 @@
         <v>17</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3866,19 +3898,19 @@
         <v>17</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>17</v>
@@ -3890,7 +3922,7 @@
         <v>17</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>17</v>
@@ -3901,21 +3933,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>17</v>
@@ -3927,16 +3959,16 @@
         <v>17</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3986,13 +4018,13 @@
         <v>17</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>17</v>
@@ -4010,7 +4042,7 @@
         <v>17</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>17</v>
@@ -4021,21 +4053,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>17</v>
@@ -4047,16 +4079,16 @@
         <v>17</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4106,19 +4138,19 @@
         <v>17</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>17</v>
@@ -4130,7 +4162,7 @@
         <v>17</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>17</v>
@@ -4141,45 +4173,45 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>17</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>17</v>
@@ -4228,19 +4260,19 @@
         <v>17</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>17</v>
@@ -4252,7 +4284,7 @@
         <v>17</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>17</v>
@@ -4263,10 +4295,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4274,10 +4306,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>17</v>
@@ -4286,20 +4318,20 @@
         <v>17</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>17</v>
@@ -4348,34 +4380,34 @@
         <v>17</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>17</v>
@@ -4383,21 +4415,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>17</v>
@@ -4406,20 +4438,20 @@
         <v>17</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>17</v>
@@ -4468,31 +4500,31 @@
         <v>17</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>17</v>
@@ -4503,21 +4535,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>17</v>
@@ -4526,19 +4558,19 @@
         <v>17</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4588,31 +4620,31 @@
         <v>17</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>17</v>
@@ -4623,10 +4655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4634,34 +4666,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>9</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>17</v>
@@ -4686,13 +4718,13 @@
         <v>17</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>17</v>
@@ -4710,34 +4742,34 @@
         <v>17</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>17</v>
@@ -4745,10 +4777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4756,13 +4788,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>17</v>
@@ -4771,19 +4803,19 @@
         <v>17</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>17</v>
@@ -4808,13 +4840,13 @@
         <v>17</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>17</v>
@@ -4832,19 +4864,19 @@
         <v>17</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>17</v>
@@ -4856,10 +4888,10 @@
         <v>17</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>17</v>
@@ -4867,45 +4899,45 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>17</v>
@@ -4930,13 +4962,13 @@
         <v>17</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>17</v>
@@ -4954,45 +4986,45 @@
         <v>17</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5000,10 +5032,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>17</v>
@@ -5015,13 +5047,13 @@
         <v>17</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5072,13 +5104,13 @@
         <v>17</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>17</v>
@@ -5096,7 +5128,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>17</v>
@@ -5107,21 +5139,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>17</v>
@@ -5133,16 +5165,16 @@
         <v>17</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5180,31 +5212,31 @@
         <v>17</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>17</v>
@@ -5216,7 +5248,7 @@
         <v>17</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>17</v>
@@ -5227,10 +5259,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5238,34 +5270,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>17</v>
@@ -5302,29 +5334,29 @@
         <v>17</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>17</v>
@@ -5333,10 +5365,10 @@
         <v>17</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>17</v>
@@ -5347,47 +5379,47 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>17</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>17</v>
@@ -5436,19 +5468,19 @@
         <v>17</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>17</v>
@@ -5457,10 +5489,10 @@
         <v>17</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>17</v>
@@ -5471,47 +5503,47 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>17</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>17</v>
@@ -5560,19 +5592,19 @@
         <v>17</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>17</v>
@@ -5581,10 +5613,10 @@
         <v>17</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>17</v>
@@ -5595,10 +5627,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5606,10 +5638,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>17</v>
@@ -5618,22 +5650,22 @@
         <v>17</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>17</v>
@@ -5682,19 +5714,19 @@
         <v>17</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>17</v>
@@ -5703,10 +5735,10 @@
         <v>17</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>17</v>
@@ -5717,10 +5749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5728,34 +5760,34 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>17</v>
@@ -5804,34 +5836,34 @@
         <v>17</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>17</v>
@@ -5839,10 +5871,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5850,10 +5882,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>17</v>
@@ -5865,13 +5897,13 @@
         <v>17</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5922,13 +5954,13 @@
         <v>17</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>17</v>
@@ -5946,7 +5978,7 @@
         <v>17</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>17</v>
@@ -5957,21 +5989,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>17</v>
@@ -5983,16 +6015,16 @@
         <v>17</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6030,31 +6062,31 @@
         <v>17</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>17</v>
@@ -6066,7 +6098,7 @@
         <v>17</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>17</v>
@@ -6077,10 +6109,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6088,31 +6120,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6162,19 +6194,19 @@
         <v>17</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>17</v>
@@ -6186,7 +6218,7 @@
         <v>17</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>17</v>
@@ -6197,10 +6229,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6208,10 +6240,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>17</v>
@@ -6220,19 +6252,19 @@
         <v>17</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6258,13 +6290,13 @@
         <v>17</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>17</v>
@@ -6282,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>17</v>
@@ -6306,7 +6338,7 @@
         <v>17</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>17</v>
@@ -6317,10 +6349,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6328,10 +6360,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>17</v>
@@ -6340,19 +6372,19 @@
         <v>17</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6402,19 +6434,19 @@
         <v>17</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>17</v>
@@ -6426,7 +6458,7 @@
         <v>17</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>17</v>
@@ -6437,10 +6469,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6448,10 +6480,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>17</v>
@@ -6460,19 +6492,19 @@
         <v>17</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6522,19 +6554,19 @@
         <v>17</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>17</v>
@@ -6546,7 +6578,7 @@
         <v>17</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>17</v>
@@ -6557,10 +6589,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6568,10 +6600,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>17</v>
@@ -6580,19 +6612,19 @@
         <v>17</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6642,19 +6674,19 @@
         <v>17</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>17</v>
@@ -6663,13 +6695,13 @@
         <v>17</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>17</v>
@@ -6677,45 +6709,45 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>17</v>
@@ -6764,34 +6796,34 @@
         <v>17</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>17</v>
@@ -6799,10 +6831,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6810,10 +6842,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>17</v>
@@ -6825,13 +6857,13 @@
         <v>17</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6882,13 +6914,13 @@
         <v>17</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>17</v>
@@ -6906,7 +6938,7 @@
         <v>17</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>17</v>
@@ -6917,21 +6949,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>17</v>
@@ -6943,16 +6975,16 @@
         <v>17</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6990,31 +7022,31 @@
         <v>17</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>17</v>
@@ -7026,7 +7058,7 @@
         <v>17</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>17</v>
@@ -7037,10 +7069,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7048,31 +7080,31 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7122,19 +7154,19 @@
         <v>17</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>17</v>
@@ -7146,7 +7178,7 @@
         <v>17</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>17</v>
@@ -7157,10 +7189,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7168,10 +7200,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>17</v>
@@ -7180,19 +7212,19 @@
         <v>17</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7218,13 +7250,13 @@
         <v>17</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>17</v>
@@ -7242,19 +7274,19 @@
         <v>17</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>17</v>
@@ -7266,7 +7298,7 @@
         <v>17</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>17</v>
@@ -7277,10 +7309,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7288,10 +7320,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>17</v>
@@ -7300,19 +7332,19 @@
         <v>17</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7362,19 +7394,19 @@
         <v>17</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>17</v>
@@ -7386,7 +7418,7 @@
         <v>17</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>17</v>
@@ -7397,10 +7429,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7408,10 +7440,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>17</v>
@@ -7420,19 +7452,19 @@
         <v>17</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7482,19 +7514,19 @@
         <v>17</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>17</v>
@@ -7506,7 +7538,7 @@
         <v>17</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>17</v>
@@ -7517,45 +7549,45 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>17</v>
@@ -7604,34 +7636,34 @@
         <v>17</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>17</v>
@@ -7639,10 +7671,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7650,10 +7682,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>17</v>
@@ -7662,19 +7694,19 @@
         <v>17</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7724,19 +7756,19 @@
         <v>17</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>17</v>
@@ -7745,13 +7777,13 @@
         <v>17</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>17</v>
@@ -7759,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7770,10 +7802,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>17</v>
@@ -7782,20 +7814,20 @@
         <v>17</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>17</v>
@@ -7844,45 +7876,45 @@
         <v>17</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7890,34 +7922,34 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>17</v>
@@ -7954,92 +7986,92 @@
         <v>17</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>17</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>17</v>
@@ -8064,13 +8096,13 @@
         <v>17</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>388</v>
+        <v>17</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>389</v>
+        <v>17</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>17</v>
@@ -8088,80 +8120,82 @@
         <v>17</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AG50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="B51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AO50" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>17</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>17</v>
@@ -8186,13 +8220,13 @@
         <v>17</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>398</v>
+        <v>17</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>399</v>
+        <v>17</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>17</v>
@@ -8210,45 +8244,45 @@
         <v>17</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>403</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8256,10 +8290,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>17</v>
@@ -8271,19 +8305,19 @@
         <v>17</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>405</v>
+        <v>237</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>17</v>
@@ -8308,13 +8342,13 @@
         <v>17</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>17</v>
+        <v>399</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>17</v>
@@ -8332,19 +8366,19 @@
         <v>17</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>17</v>
+        <v>400</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>17</v>
@@ -8353,10 +8387,10 @@
         <v>17</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>410</v>
+        <v>188</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>17</v>
@@ -8367,21 +8401,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>17</v>
+        <v>403</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>17</v>
@@ -8393,18 +8427,20 @@
         <v>17</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>17</v>
       </c>
@@ -8428,13 +8464,13 @@
         <v>17</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>17</v>
@@ -8452,45 +8488,45 @@
         <v>17</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AG53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AO53" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8498,10 +8534,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>17</v>
@@ -8513,19 +8549,19 @@
         <v>17</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>236</v>
+        <v>415</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>17</v>
@@ -8550,13 +8586,13 @@
         <v>17</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>427</v>
+        <v>17</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>428</v>
+        <v>17</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>17</v>
@@ -8574,19 +8610,19 @@
         <v>17</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>17</v>
@@ -8595,10 +8631,10 @@
         <v>17</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>17</v>
@@ -8609,10 +8645,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8620,10 +8656,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>17</v>
@@ -8635,16 +8671,16 @@
         <v>17</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>432</v>
+        <v>237</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8670,13 +8706,13 @@
         <v>17</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>17</v>
+        <v>426</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>17</v>
+        <v>427</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>17</v>
@@ -8694,45 +8730,45 @@
         <v>17</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8740,10 +8776,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>17</v>
@@ -8755,18 +8791,20 @@
         <v>17</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>441</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>17</v>
       </c>
@@ -8790,13 +8828,13 @@
         <v>17</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>17</v>
+        <v>437</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>17</v>
+        <v>438</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>17</v>
@@ -8814,45 +8852,45 @@
         <v>17</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AO56" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>448</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8860,10 +8898,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>17</v>
@@ -8875,20 +8913,18 @@
         <v>17</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>17</v>
       </c>
@@ -8936,45 +8972,45 @@
         <v>17</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8982,10 +9018,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>17</v>
@@ -8997,15 +9033,17 @@
         <v>17</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>451</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>103</v>
+        <v>452</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>17</v>
@@ -9054,37 +9092,37 @@
         <v>17</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>105</v>
+        <v>450</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>17</v>
+        <v>455</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>17</v>
+        <v>456</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>106</v>
+        <v>457</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>17</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9096,14 +9134,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>17</v>
@@ -9115,18 +9153,20 @@
         <v>17</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>110</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>111</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>17</v>
       </c>
@@ -9174,19 +9214,19 @@
         <v>17</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>116</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>117</v>
+        <v>465</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>17</v>
@@ -9195,10 +9235,10 @@
         <v>17</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>17</v>
+        <v>466</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>106</v>
+        <v>467</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>17</v>
@@ -9209,46 +9249,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>461</v>
+        <v>17</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>462</v>
+        <v>104</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>17</v>
       </c>
@@ -9296,19 +9332,19 @@
         <v>17</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>106</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>17</v>
@@ -9320,7 +9356,7 @@
         <v>17</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>17</v>
@@ -9331,21 +9367,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>17</v>
@@ -9357,15 +9393,17 @@
         <v>17</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>466</v>
+        <v>110</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>111</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>17</v>
@@ -9414,19 +9452,19 @@
         <v>17</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>117</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>469</v>
+        <v>17</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>17</v>
@@ -9435,10 +9473,10 @@
         <v>17</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>17</v>
@@ -9449,42 +9487,46 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>17</v>
+        <v>471</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>110</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>17</v>
       </c>
@@ -9532,19 +9574,19 @@
         <v>17</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>469</v>
+        <v>17</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>17</v>
@@ -9553,10 +9595,10 @@
         <v>17</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>17</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>475</v>
+        <v>188</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>17</v>
@@ -9567,10 +9609,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9578,10 +9620,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>17</v>
@@ -9593,7 +9635,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>236</v>
+        <v>476</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>477</v>
@@ -9601,12 +9643,8 @@
       <c r="M63" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>480</v>
-      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>17</v>
       </c>
@@ -9630,55 +9668,55 @@
         <v>17</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>17</v>
@@ -9689,10 +9727,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9700,10 +9738,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>17</v>
@@ -9715,20 +9753,16 @@
         <v>17</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>236</v>
+        <v>476</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>17</v>
       </c>
@@ -9752,13 +9786,13 @@
         <v>17</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>490</v>
+        <v>17</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>491</v>
+        <v>17</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>17</v>
@@ -9776,31 +9810,31 @@
         <v>17</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>17</v>
@@ -9811,10 +9845,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9822,10 +9856,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>17</v>
@@ -9837,17 +9871,19 @@
         <v>17</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>237</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>17</v>
@@ -9872,13 +9908,13 @@
         <v>17</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>17</v>
+        <v>491</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>17</v>
+        <v>492</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>17</v>
@@ -9896,31 +9932,31 @@
         <v>17</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>17</v>
+        <v>493</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>17</v>
+        <v>494</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>17</v>
@@ -9931,10 +9967,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9942,10 +9978,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>17</v>
@@ -9957,16 +9993,20 @@
         <v>17</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>17</v>
       </c>
@@ -9990,13 +10030,13 @@
         <v>17</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>17</v>
+        <v>500</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>17</v>
+        <v>501</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>17</v>
@@ -10014,31 +10054,31 @@
         <v>17</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>17</v>
+        <v>493</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>412</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>17</v>
@@ -10060,10 +10100,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>17</v>
@@ -10072,7 +10112,7 @@
         <v>17</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>503</v>
@@ -10083,10 +10123,10 @@
       <c r="M67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>17</v>
       </c>
@@ -10137,16 +10177,16 @@
         <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>17</v>
@@ -10155,10 +10195,10 @@
         <v>17</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>17</v>
@@ -10169,10 +10209,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10180,10 +10220,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>17</v>
@@ -10192,20 +10232,18 @@
         <v>17</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>513</v>
-      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>17</v>
@@ -10254,19 +10292,19 @@
         <v>17</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>17</v>
@@ -10275,10 +10313,10 @@
         <v>17</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>17</v>
@@ -10289,10 +10327,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10300,10 +10338,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>17</v>
@@ -10312,23 +10350,21 @@
         <v>17</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>450</v>
+        <v>513</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>519</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>17</v>
       </c>
@@ -10376,19 +10412,19 @@
         <v>17</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>17</v>
@@ -10397,10 +10433,10 @@
         <v>17</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>17</v>
@@ -10411,10 +10447,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10422,10 +10458,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>17</v>
@@ -10434,18 +10470,20 @@
         <v>17</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>102</v>
+        <v>520</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>103</v>
+        <v>521</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>17</v>
@@ -10494,19 +10532,19 @@
         <v>17</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>105</v>
+        <v>519</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>17</v>
@@ -10515,10 +10553,10 @@
         <v>17</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>17</v>
+        <v>517</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>106</v>
+        <v>524</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>17</v>
@@ -10529,21 +10567,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>17</v>
@@ -10552,21 +10590,23 @@
         <v>17</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>109</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>110</v>
+        <v>526</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>111</v>
+        <v>527</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>17</v>
       </c>
@@ -10614,19 +10654,19 @@
         <v>17</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>116</v>
+        <v>525</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>17</v>
@@ -10635,10 +10675,10 @@
         <v>17</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>17</v>
+        <v>530</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>106</v>
+        <v>531</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>17</v>
@@ -10649,46 +10689,42 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>461</v>
+        <v>17</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>462</v>
+        <v>104</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>17</v>
       </c>
@@ -10736,19 +10772,19 @@
         <v>17</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>464</v>
+        <v>106</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>17</v>
@@ -10760,7 +10796,7 @@
         <v>17</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>17</v>
@@ -10771,21 +10807,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>17</v>
@@ -10794,23 +10830,21 @@
         <v>17</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>236</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>527</v>
+        <v>112</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>17</v>
       </c>
@@ -10834,13 +10868,13 @@
         <v>17</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>251</v>
+        <v>17</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>17</v>
@@ -10858,34 +10892,34 @@
         <v>17</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>529</v>
+        <v>17</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>254</v>
+        <v>17</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>256</v>
+        <v>17</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>17</v>
@@ -10893,45 +10927,45 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>17</v>
+        <v>471</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>373</v>
+        <v>110</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>532</v>
+        <v>113</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>377</v>
+        <v>195</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>17</v>
@@ -10980,45 +11014,45 @@
         <v>17</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>533</v>
+        <v>17</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>380</v>
+        <v>17</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>381</v>
+        <v>188</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>382</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11026,10 +11060,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>17</v>
@@ -11038,22 +11072,22 @@
         <v>17</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>387</v>
+        <v>250</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>17</v>
@@ -11078,13 +11112,13 @@
         <v>17</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>388</v>
+        <v>251</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>389</v>
+        <v>252</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>17</v>
@@ -11102,34 +11136,34 @@
         <v>17</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>17</v>
+        <v>539</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>391</v>
+        <v>256</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>17</v>
+        <v>257</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>17</v>
@@ -11137,21 +11171,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>393</v>
+        <v>17</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>17</v>
@@ -11160,22 +11194,22 @@
         <v>17</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>236</v>
+        <v>374</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>394</v>
+        <v>541</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>396</v>
+        <v>542</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>17</v>
@@ -11200,13 +11234,13 @@
         <v>17</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>398</v>
+        <v>17</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>399</v>
+        <v>17</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>17</v>
@@ -11224,45 +11258,45 @@
         <v>17</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>400</v>
+        <v>543</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>403</v>
+        <v>384</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11270,10 +11304,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>17</v>
@@ -11285,19 +11319,19 @@
         <v>17</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>453</v>
+        <v>547</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>454</v>
+        <v>397</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>17</v>
@@ -11322,13 +11356,13 @@
         <v>17</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>17</v>
+        <v>399</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>17</v>
@@ -11346,19 +11380,19 @@
         <v>17</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>17</v>
+        <v>400</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>17</v>
@@ -11367,20 +11401,264 @@
         <v>17</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>456</v>
+        <v>188</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>457</v>
+        <v>401</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>17</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP77">
+  <autoFilter ref="A1:AP79">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11390,7 +11668,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11</t>
+    <t>2025-12-17</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/StructureDefinition-ISiKLebensZustand.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.1-rc</t>
   </si>
   <si>
     <t>Name</t>
